--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-rios.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-rios.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>10243.33</v>
+        <v>10070.27</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-rios.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,65 +514,126 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2282-94-CM25</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>69.200.100-1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>SOSAFE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>76.376.088-k</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>67034.67999999999</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>1057547-8632-SE26</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>2239-19-LR23</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>jun-2026</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>61.607.502-0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Los Ríos</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M3" s="2" t="n">
         <v>10070.27</v>
       </c>
     </row>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-rios.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-rios.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Los Ríos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Los Ríos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -625,7 +625,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-rios.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2282-94-CM25</t>
+          <t>1057547-17093-SE25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,86 +554,935 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>67034.67999999999</v>
+        <v>46709.67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>1057547-21069-SE25</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>46743.26</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2282-94-CM25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>69.200.100-1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>SOSAFE</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>76.376.088-k</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>67034.67999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1057547-23023-SE25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>47002.28</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1057547-24798-SE25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>47226.81</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1057547-26417-SE25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>45570.52</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1057547-28151-SE25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>45677.45</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1057547-33585-SE25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>45973.97</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1057547-34456-SE25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>46931.4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1057547-43948-SE25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>47562.28</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1057547-44916-SE25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>48499.76</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1057547-1927-SE26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>50881.98</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1057547-4819-SE26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>47438.21</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1057547-5944-SE26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>49532.62</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>1057547-8632-SE26</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>2239-19-LR23</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>jun-2026</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>61.607.502-0</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Los Ríos</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="M16" s="2" t="n">
         <v>10070.27</v>
       </c>
     </row>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-rios.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-rios.xlsx
@@ -1444,7 +1444,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-rios.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1486,6 +1486,71 @@
         <v>10070.27</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1057547-15634-SE26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>17302.97</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
